--- a/Resources/O3/EMR-DHIS2 Tracker O3 Neonatal Mapping.xlsx
+++ b/Resources/O3/EMR-DHIS2 Tracker O3 Neonatal Mapping.xlsx
@@ -30,4080 +30,8228 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMC ward follow up sheet</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abdominal Distension [KMC ward follow up sheet]</t>
+          <t xml:space="preserve">Advice given on discharge [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abdominal Distension</t>
+          <t xml:space="preserve">Advice given on discharge</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMC ward follow up sheet</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Age  in days (At admission to KMC ward) [KMC ward follow up sheet]</t>
+          <t xml:space="preserve">Age at discharge [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Age  in days (At admission to KMC ward)</t>
+          <t xml:space="preserve">Age at discharge</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMC ward follow up sheet</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bleeding from the stamp or cut [KMC ward follow up sheet]</t>
+          <t xml:space="preserve">Any significant maternal and birth history [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bleeding from the stamp or cut</t>
+          <t xml:space="preserve">Any significant maternal and birth history</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMC ward follow up sheet</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convulsion [KMC ward follow up sheet]</t>
+          <t xml:space="preserve">Appointment date [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convulsion</t>
+          <t xml:space="preserve">Appointment date</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMC ward follow up sheet</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danger sign present [KMC ward follow up sheet]</t>
+          <t xml:space="preserve">Corrected GA at discharges [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danger sign present</t>
+          <t xml:space="preserve">Corrected GA at discharges</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMC ward follow up sheet</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Family planning [KMC ward follow up sheet]</t>
+          <t xml:space="preserve">Course and Treatments given in the hospital [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Family planning</t>
+          <t xml:space="preserve">Course and Treatments given in the hospital</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMC ward follow up sheet</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feeding intolerance [KMC ward follow up sheet]</t>
+          <t xml:space="preserve">Date and time of discharge [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feeding intolerance</t>
+          <t xml:space="preserve">Date and time of discharge</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMC ward follow up sheet</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fever ≥37.5 [KMC ward follow up sheet]</t>
+          <t xml:space="preserve">Discharge Outcome [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fever ≥37.5</t>
+          <t xml:space="preserve">Discharge Outcome n</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMC ward follow up sheet</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Floppy or stiff [KMC ward follow up sheet]</t>
+          <t xml:space="preserve">Final Discharge Diagnosis/Cause of Death (primary) [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Floppy or stiff</t>
+          <t xml:space="preserve">Final Discharge Diagnosis/Cause of Death</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMC ward follow up sheet</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gain in gm/kg/day [KMC ward follow up sheet]</t>
+          <t xml:space="preserve">Final Discharge Diagnosis/Cause of Death (Secondary) [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gain in gm/kg/day</t>
+          <t xml:space="preserve">Final Discharge Diagnosis/Cause of Death</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMC ward follow up sheet</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Head circumference(Weekly) [KMC ward follow up sheet]</t>
+          <t xml:space="preserve">GA [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Head circumference(Weekly)</t>
+          <t xml:space="preserve">GA n</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMC ward follow up sheet</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hours on KMC/every 6hours [KMC ward follow up sheet]</t>
+          <t xml:space="preserve">HC on discharge [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hours on KMC/every 6hours</t>
+          <t xml:space="preserve">HC on discharge</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMC ward follow up sheet</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">If present frequency [KMC ward follow up sheet]</t>
+          <t xml:space="preserve">If infection - is it hospital-acquired(secondary)? [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">If present frequency</t>
+          <t xml:space="preserve">If infection - is it hospital-acquired n</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMC ward follow up sheet</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mode of feeding kmc [KMC ward follow up sheet]</t>
+          <t xml:space="preserve">If infection - is it hospital-acquired? [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mode of feeding kmc</t>
+          <t xml:space="preserve">If infection - is it hospital-acquired n</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMC ward follow up sheet</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name and  signature [KMC ward follow up sheet]</t>
+          <t xml:space="preserve">If Other Cause of Death or Final Diagnosis - Specify [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name and  signature</t>
+          <t xml:space="preserve">If Other Cause of Death or Final Diagnosis - Specify n</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMC ward follow up sheet</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number of wet diaper [KMC ward follow up sheet]</t>
+          <t xml:space="preserve">If Other Cause of Death or Final Diagnosis - Specify(secondary): [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number of wet diaper</t>
+          <t xml:space="preserve">If Other Cause of Death or Final Diagnosis - Specify n</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMC ward follow up sheet</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other danger sign [KMC ward follow up sheet]</t>
+          <t xml:space="preserve">If other congenital cause/diagnosis - specify [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other danger sign</t>
+          <t xml:space="preserve">If other congenital cause/diagnosis - specify n</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMC ward follow up sheet</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pallor [KMC ward follow up sheet]</t>
+          <t xml:space="preserve">If other congenital cause/diagnosis - specify(secondary): [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pallor</t>
+          <t xml:space="preserve">If other congenital cause/diagnosis - specify n</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMC ward follow up sheet</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plan kmc [KMC ward follow up sheet]</t>
+          <t xml:space="preserve">If other infection cause/diagnosis - specify [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plan kmc</t>
+          <t xml:space="preserve">If other infection cause/diagnosis - specify n</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMC ward follow up sheet</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stool color [KMC ward follow up sheet]</t>
+          <t xml:space="preserve">If other infection cause/diagnosis - specify(secondary): [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stool color</t>
+          <t xml:space="preserve">If other infection cause/diagnosis - specify n</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMC ward follow up sheet</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Temperature &lt; 36.5 or not raising after warming [KMC ward follow up sheet]</t>
+          <t xml:space="preserve">If other intrapartum-related cause/diagnosis - specify [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Temperature &lt; 36.5 or not raising after warming</t>
+          <t xml:space="preserve">If other intrapartum-related cause/diagnosis - specify n</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMC ward follow up sheet</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Total KMC hours/day [KMC ward follow up sheet]</t>
+          <t xml:space="preserve">If other intrapartum-related cause/diagnosis - specify(secondary): [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Total KMC hours/day</t>
+          <t xml:space="preserve">If other intrapartum-related cause/diagnosis - specify n</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMC ward follow up sheet</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Type of feed [KMC ward follow up sheet]</t>
+          <t xml:space="preserve">If other prematurity cause/diagnosis - specify [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Type of feed</t>
+          <t xml:space="preserve">If other prematurity cause/diagnosis - specify n</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMC ward follow up sheet</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umbilicus draining pus [KMC ward follow up sheet]</t>
+          <t xml:space="preserve">If other prematurity cause/diagnosis - specify(secondary): [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umbilicus draining pus</t>
+          <t xml:space="preserve">If other prematurity cause/diagnosis - specify n</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMC ward follow up sheet</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Urine [KMC ward follow up sheet]</t>
+          <t xml:space="preserve">Investigations done and result [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Urine</t>
+          <t xml:space="preserve">Investigations done and result</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMC ward follow up sheet</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vaccination [KMC ward follow up sheet]</t>
+          <t xml:space="preserve">Length on discharge [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vaccination</t>
+          <t xml:space="preserve">Length on discharge</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMC ward follow up sheet</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weight (At admission to KMC ward) [KMC ward follow up sheet]</t>
+          <t xml:space="preserve">List of diagnosis [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weight (At admission to KMC ward)</t>
+          <t xml:space="preserve">List of diagnosis</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abortion (Induced) [Neonatal referral form]</t>
+          <t xml:space="preserve">Medications/Supplements given on discharge [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abortion (Induced) ref</t>
+          <t xml:space="preserve">Medications/Supplements given on discharge</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abortion (Spontaneous) [Neonatal referral form]</t>
+          <t xml:space="preserve">Name of physician [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abortion (Spontaneous) ref</t>
+          <t xml:space="preserve">Name of physician dis</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">APGAR score: 10th min [Neonatal referral form]</t>
+          <t xml:space="preserve">Newborn status at discharge [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">APGAR score: 10th min</t>
+          <t xml:space="preserve">Newborn status at discharge n</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">APGAR score: 1st min [Neonatal referral form]</t>
+          <t xml:space="preserve">Pertinent physical examination finding at discharge [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">APGAR score: 1st min</t>
+          <t xml:space="preserve">Pertinent Physical examination finding at discharge</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">APGAR score: 20th min [Neonatal referral form]</t>
+          <t xml:space="preserve">Place of follow up [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">APGAR score: 20th min</t>
+          <t xml:space="preserve">Place of follow up</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">APGAR score: 5th min [Neonatal referral form]</t>
+          <t xml:space="preserve">PR [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">APGAR score: 5th min</t>
+          <t xml:space="preserve">PR n dis</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baby dried thoroughly at birth [Neonatal referral form]</t>
+          <t xml:space="preserve">Reason for follow up [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baby dried thoroughly at birth</t>
+          <t xml:space="preserve">Reason for follow up</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baby placed in iKMC [Neonatal referral form]</t>
+          <t xml:space="preserve">RR [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baby placed in iKMC</t>
+          <t xml:space="preserve">RR n dis</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baby placed in plastic bag [Neonatal referral form]</t>
+          <t xml:space="preserve">Sao2 [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baby placed in plastic bag</t>
+          <t xml:space="preserve">Sao2 n dis</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baby placed on CPAP [Neonatal referral form]</t>
+          <t xml:space="preserve">Sub-Categories of Congenital Malformations [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baby placed on CPAP</t>
+          <t xml:space="preserve">Sub-Categories of Congenital Malformations n</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baby placed skin to skin at birth [Neonatal referral form]</t>
+          <t xml:space="preserve">Sub-Categories of Congenital Malformations(secondary): [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baby placed skin to skin at birth</t>
+          <t xml:space="preserve">Sub-Categories of Congenital Malformations n</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bag and Mask [Neonatal referral form]</t>
+          <t xml:space="preserve">Sub-Categories of Infection [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bag and Mask</t>
+          <t xml:space="preserve">Sub-Categories of Infection n</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blood group done [Neonatal referral form]</t>
+          <t xml:space="preserve">Sub-Categories of Intrapartum-Related [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blood group done ref</t>
+          <t xml:space="preserve">Sub-Categories of Intrapartum-Related n</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chest compression [Neonatal referral form]</t>
+          <t xml:space="preserve">Sub-Categories of Intrapartum-Related(secondary): [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chest compression</t>
+          <t xml:space="preserve">Sub-Categories of Intrapartum-Related n</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chlorhexdine 4% [Neonatal referral form]</t>
+          <t xml:space="preserve">Sub-Categories of Jaundice (Pathological) [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chlorhexdine 4%</t>
+          <t xml:space="preserve">Sub-Categories of Jaundice (Pathological) n</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date of referral [Neonatal referral form]</t>
+          <t xml:space="preserve">Sub-Categories of Jaundice (Pathological)(secondary): [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date of referral</t>
+          <t xml:space="preserve">Sub-Categories of Jaundice (Pathological) n</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delayed Cord clamping done [Neonatal referral form]</t>
+          <t xml:space="preserve">Sub-Categories of Prematurity [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delayed Cord clamping done</t>
+          <t xml:space="preserve">Sub-Categories of Prematurity n</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery [Neonatal referral form]</t>
+          <t xml:space="preserve">Sub-Categories of Prematurity(secondary): [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery n</t>
+          <t xml:space="preserve">Sub-Categories of Prematurity n</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery attended by provider trained on HBB/ neonatal resuscitation? [Neonatal referral form]</t>
+          <t xml:space="preserve">Temp [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery attended by provider trained on HBB/ neonatal resuscitation</t>
+          <t xml:space="preserve">Temp n dis</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duration [Neonatal referral form]</t>
+          <t xml:space="preserve">Type of feeding on discharge [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duration n</t>
+          <t xml:space="preserve">Type of feeding on discharge</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duration of resuscitation [Neonatal referral form]</t>
+          <t xml:space="preserve">Vaccinations given date [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duration of resuscitation</t>
+          <t xml:space="preserve">Vaccinations given date</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duration of ROM [Neonatal referral form]</t>
+          <t xml:space="preserve">Vaccinations type given [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duration of ROM</t>
+          <t xml:space="preserve">Vaccinations type given</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early Neonatal death [Neonatal referral form]</t>
+          <t xml:space="preserve">Weight on discharge [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early Neonatal death ref</t>
+          <t xml:space="preserve">Weight on discharge</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">Discharge care form</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Epinephrine doses [Neonatal referral form]</t>
+          <t xml:space="preserve">what was done to prevent death [Neonatal Discharge care form]</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Epinephrine doses</t>
+          <t xml:space="preserve">what was done to prevent death</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estimated by: Obstetric Ultrasound [Neonatal referral form]</t>
+          <t xml:space="preserve">Abdominal Distension [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estimated by: Obstetric Ultrasound ref</t>
+          <t xml:space="preserve">Abdominal Distension</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feeding initiated [Neonatal referral form]</t>
+          <t xml:space="preserve">Age  in days (At admission to KMC ward) [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feeding initiated</t>
+          <t xml:space="preserve">Age  in days (At admission to KMC ward)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fluid administered [Neonatal referral form]</t>
+          <t xml:space="preserve">Assessment [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fluid administered</t>
+          <t xml:space="preserve">Assessment kmc</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gestational age (days) [Neonatal referral form]</t>
+          <t xml:space="preserve">Bleeding from the stamp or cut [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gestational age (days) ref</t>
+          <t xml:space="preserve">Bleeding from the stamp or cut</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gestational age (weeks) [Neonatal referral form]</t>
+          <t xml:space="preserve">Convulsion [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gestational age (weeks) ref</t>
+          <t xml:space="preserve">Convulsion</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">If done tick what was done [Neonatal referral form]</t>
+          <t xml:space="preserve">Danger sign present [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">If done tick what was done</t>
+          <t xml:space="preserve">Danger sign present</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">If Obstetric Ultrasound, done at ref [Neonatal referral form]</t>
+          <t xml:space="preserve">DLT/NLT [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">If Obstetric Ultrasound, done at ref</t>
+          <t xml:space="preserve">DLT or NLT kmc followup</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">If yes Duration [Neonatal referral form]</t>
+          <t xml:space="preserve">Family planning [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">If yes Duration ref</t>
+          <t xml:space="preserve">Family planning</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">If yes, number of doses [Neonatal referral form]</t>
+          <t xml:space="preserve">Feeding intolerance [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">If yes, number of doses ref</t>
+          <t xml:space="preserve">Feeding intolerance</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">If yes, on HAART [Neonatal referral form]</t>
+          <t xml:space="preserve">Fever ≥37.5 [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">If yes, on HAART ref</t>
+          <t xml:space="preserve">Fever ≥37.5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indication [Neonatal referral form]</t>
+          <t xml:space="preserve">Floppy or stiff [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indication n</t>
+          <t xml:space="preserve">Floppy or stiff</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Infant prophylaxis started [Neonatal referral form]</t>
+          <t xml:space="preserve">Gain in gm/kg/day [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Infant prophylaxis started ref</t>
+          <t xml:space="preserve">Gain in gm/kg/day</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intra/Inter facility transfer [Neonatal referral form]</t>
+          <t xml:space="preserve">Head circumference(Weekly) [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intra/Inter facility transfer</t>
+          <t xml:space="preserve">Head circumference(Weekly)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Investigation result [Neonatal referral form]</t>
+          <t xml:space="preserve">Hours on KMC/every 6hours [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Investigation result</t>
+          <t xml:space="preserve">Hours on KMC/every 6hours</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal Age [Neonatal referral form]</t>
+          <t xml:space="preserve">HR [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal Age n</t>
+          <t xml:space="preserve">HR kmc f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal MRN [Neonatal referral form]</t>
+          <t xml:space="preserve">If present frequency [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal MRN n</t>
+          <t xml:space="preserve">If present frequency</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meconium sucked from oropharynx [Neonatal referral form]</t>
+          <t xml:space="preserve">Jaundice [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meconium sucked from oropharynx</t>
+          <t xml:space="preserve">Jaundice kmc f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name of clinician [Neonatal referral form]</t>
+          <t xml:space="preserve">Mode of feeding kmc [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name of clinician</t>
+          <t xml:space="preserve">Mode of feeding kmc</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name of Referring Facility [Neonatal referral form]</t>
+          <t xml:space="preserve">Name and  signature [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name of Referring Facility</t>
+          <t xml:space="preserve">Name and  signature</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal resuscitation done [Neonatal referral form]</t>
+          <t xml:space="preserve">Number of wet diaper [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal resuscitation done</t>
+          <t xml:space="preserve">Number of wet diaper</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other treatment given [Neonatal referral form]</t>
+          <t xml:space="preserve">Other danger sign [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other treatment given</t>
+          <t xml:space="preserve">Other danger sign</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">place of ANC follow up [Neonatal referral form]</t>
+          <t xml:space="preserve">Pallor [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">place of ANC follow up ref</t>
+          <t xml:space="preserve">Pallor</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pregnancy related maternal problem [Neonatal referral form]</t>
+          <t xml:space="preserve">Plan kmc [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pregnancy related maternal problem ref</t>
+          <t xml:space="preserve">Plan kmc</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reason for NICU referral [Neonatal referral form]</t>
+          <t xml:space="preserve">Provided amount of breast milk (ml/kg/day) [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reason for NICU referral</t>
+          <t xml:space="preserve">Provided amount of breast milk</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Singleton-Multiple [Neonatal referral form]</t>
+          <t xml:space="preserve">RR [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Singleton-Multiple</t>
+          <t xml:space="preserve">RR kmc f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transferred to [Neonatal referral form]</t>
+          <t xml:space="preserve">SPO2 (when needed) [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transferred to</t>
+          <t xml:space="preserve">SPO2 kmc f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">TTC Eye prophylaxis given [Neonatal referral form]</t>
+          <t xml:space="preserve">Stool [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">TTC Eye prophylaxis given</t>
+          <t xml:space="preserve">Stool kmc f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viral load/date [Neonatal referral form]</t>
+          <t xml:space="preserve">Stool color [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viral load/date ref</t>
+          <t xml:space="preserve">Stool color</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vital signs on referral HR [Neonatal referral form]</t>
+          <t xml:space="preserve">Supplement [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vital signs on referral HR</t>
+          <t xml:space="preserve">Supplement kmc f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vital signs on referral RR [Neonatal referral form]</t>
+          <t xml:space="preserve">Temperature &lt; 36.5 or not raising after warming [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vital signs on referral RR</t>
+          <t xml:space="preserve">Temperature &lt; 36.5 or not raising after warming</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vital signs on referral Saturation [Neonatal referral form]</t>
+          <t xml:space="preserve">Temperature [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vital signs on referral Saturation</t>
+          <t xml:space="preserve">Temperature kmc f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vital signs on referral Temp (c) [Neonatal referral form]</t>
+          <t xml:space="preserve">Total KMC hours/day [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vital signs on referral Temp (c)</t>
+          <t xml:space="preserve">Total KMC hours/day</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonatal referral form</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitamin K given [Neonatal referral form]</t>
+          <t xml:space="preserve">Type of feed [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitamin K given</t>
+          <t xml:space="preserve">Type of feed</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abortion(Induced) [NICU Admission Careform]</t>
+          <t xml:space="preserve">Umbilicus draining pus [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abortion(Induced)</t>
+          <t xml:space="preserve">Umbilicus draining pus</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abortion(Spontaneous) [NICU Admission Careform]</t>
+          <t xml:space="preserve">Urine [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abortion(Spontaneous)</t>
+          <t xml:space="preserve">Urine</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admission age unit [NICU Admission Careform]</t>
+          <t xml:space="preserve">Vaccination [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admission age unit n</t>
+          <t xml:space="preserve">Vaccination</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">amenorrheic for how many months [NICU Admission Careform]</t>
+          <t xml:space="preserve">Vomiting [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">amenorrheic for how many months</t>
+          <t xml:space="preserve">Vomiting kmc f</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amniotic fluid was [NICU Admission Careform]</t>
+          <t xml:space="preserve">Weight (At admission to KMC ward) [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amniotic fluid was</t>
+          <t xml:space="preserve">Weight (At admission to KMC ward)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">KMC ward follow up sheet</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANC visit [NICU Admission Careform]</t>
+          <t xml:space="preserve">Weight [KMC ward follow up sheet]</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANC visit</t>
+          <t xml:space="preserve">Weight kmc</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Any abnormality from System Examination? [NICU Admission Careform]</t>
+          <t xml:space="preserve">Antibiotics administered? [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Any abnormality from System Examination</t>
+          <t xml:space="preserve">Antibiotics administered?</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">APGAR score 10th min [NICU Admission Careform]</t>
+          <t xml:space="preserve">Apnea Prevention/Treatment [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">APGAR score 10th min</t>
+          <t xml:space="preserve">Apnea Prevention/Treatment</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">APGAR score 1st min [NICU Admission Careform]</t>
+          <t xml:space="preserve">Bed No. [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">APGAR score 1st min</t>
+          <t xml:space="preserve">Bed No</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">APGAR score 5th min [NICU Admission Careform]</t>
+          <t xml:space="preserve">Bed No. [Neonatal Medication Adminstration Sheet]</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">APGAR score 5th min</t>
+          <t xml:space="preserve">Bed No</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">APGAR score known? [NICU Admission Careform]</t>
+          <t xml:space="preserve">Date [Neonatal Medication Adminstration Sheet]</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">APGAR score known</t>
+          <t xml:space="preserve">Date n</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asphyxia [NICU Admission Careform]</t>
+          <t xml:space="preserve">Date of Amikacin administration [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asphyxia</t>
+          <t xml:space="preserve">Date of Amikacin administration</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asphyxia stage [NICU Admission Careform]</t>
+          <t xml:space="preserve">Date of Amoxicillin administration [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asphyxia stage</t>
+          <t xml:space="preserve">Date of Amoxicillin administration</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ballard score [NICU Admission Careform]</t>
+          <t xml:space="preserve">Date of Ampicillin administration [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ballard score</t>
+          <t xml:space="preserve">Date of Ampicillin administration</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birth weight category [NICU Admission Careform]</t>
+          <t xml:space="preserve">Date of Benzathine Penicillin administration [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birth weight category</t>
+          <t xml:space="preserve">Date of Benzathine Penicillin administration</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blood group and Rh [NICU Admission Careform]</t>
+          <t xml:space="preserve">Date of Cefalexin administration [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blood group and Rh n</t>
+          <t xml:space="preserve">Date of Cefalexin administration</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Breastfeeding initiated within 1 hr of birth [NICU Admission Careform]</t>
+          <t xml:space="preserve">Date of Cefixime administration [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Breastfeeding initiated within 1 hr of birth</t>
+          <t xml:space="preserve">Date of Cefixime administration</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">CENTRAL NERVOUS SYSTEM [NICU Admission Careform]</t>
+          <t xml:space="preserve">Date of Cefotaxime administration [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">CENTRAL NERVOUS SYSTEM</t>
+          <t xml:space="preserve">Date of Cefotaxime administration</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cord Chlorhexidine Administered [NICU Admission Careform]</t>
+          <t xml:space="preserve">Date of Ceftazidime administration [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cord Chlorhexidine Administered</t>
+          <t xml:space="preserve">Date of Ceftazidime administration</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date of Admission [NICU Admission Careform]</t>
+          <t xml:space="preserve">Date of Ceftriaxone administration [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date of Admission n</t>
+          <t xml:space="preserve">Date of Ceftriaxone administration</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date of delivery [NICU Admission Careform]</t>
+          <t xml:space="preserve">Date of Ciprofloxacin administration [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date of delivery</t>
+          <t xml:space="preserve">Date of Ciprofloxacin administration</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Day/Night Local time [NICU Admission Careform]</t>
+          <t xml:space="preserve">Date of Clindamycin administration [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Day/Night Local time</t>
+          <t xml:space="preserve">Date of Clindamycin administration</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Downes: Air Entry [NICU Admission Careform]</t>
+          <t xml:space="preserve">Date of Cloxacillin administration [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Downes Air Entry</t>
+          <t xml:space="preserve">Date of Cloxacillin administration</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Downes: Cyanosis [NICU Admission Careform]</t>
+          <t xml:space="preserve">Date of Crystalline Penicillin administration [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Downes Cyanosis</t>
+          <t xml:space="preserve">Date of Crystalline Penicillin administration</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Downes: Grunting [NICU Admission Careform]</t>
+          <t xml:space="preserve">Date of Flucloxacillin administration [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Downes Grunting</t>
+          <t xml:space="preserve">Date of Flucloxacillin administration</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Downes: Respiratory Rate [NICU Admission Careform]</t>
+          <t xml:space="preserve">Date of Gentamicin administration [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Downes Respiratory Rate</t>
+          <t xml:space="preserve">Date of Gentamicin administration</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Downes: Retractions [NICU Admission Careform]</t>
+          <t xml:space="preserve">Date of Levofloxacin administration [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Downes Retractions</t>
+          <t xml:space="preserve">Date of Levofloxacin administration</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duration of rapture of membrane (in hrs) [NICU Admission Careform]</t>
+          <t xml:space="preserve">Date of Meropenem administration [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duration of rapture of membrane</t>
+          <t xml:space="preserve">Date of Meropenem administration</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dysmorphic feature [NICU Admission Careform]</t>
+          <t xml:space="preserve">Date of Metronidazole administration [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dysmorphic feature</t>
+          <t xml:space="preserve">Date of Metronidazole administration</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dysmorphysim [NICU Admission Careform]</t>
+          <t xml:space="preserve">Date of OTHER antibiotic administration [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dysmorphysim</t>
+          <t xml:space="preserve">Date of OTHER antibiotic administration</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">GA by U/S [NICU Admission Careform]</t>
+          <t xml:space="preserve">Date of Piperazine administration [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">GA by U/S</t>
+          <t xml:space="preserve">Date of Piperazine administration</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">General appearance [NICU Admission Careform]</t>
+          <t xml:space="preserve">Date of Tazobactam administration [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">General appearance</t>
+          <t xml:space="preserve">Date of Tazobactam administration</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">GENITALIA [NICU Admission Careform]</t>
+          <t xml:space="preserve">Date of Vancomycin administration [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">GENITALIA n</t>
+          <t xml:space="preserve">Date of Vancomycin administration</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Head circumference (cm) [NICU Admission Careform]</t>
+          <t xml:space="preserve">Discontinuation  Date [Neonatal Medication Adminstration Sheet]</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Head circumference n</t>
+          <t xml:space="preserve">Discontinuation  Date</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">hours prior to delivery [NICU Admission Careform]</t>
+          <t xml:space="preserve">Does the infant receive mechanical ventilation? [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">hours prior to delivery</t>
+          <t xml:space="preserve">Does the infant receive mechanical ventilation?</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">If Resuscitated, tick what was done [NICU Admission Careform]</t>
+          <t xml:space="preserve">Dose [Neonatal Medication Adminstration Sheet]</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">If Resuscitated, tick what was done</t>
+          <t xml:space="preserve">Dose n</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">if Unknown [NICU Admission Careform]</t>
+          <t xml:space="preserve">First dose time [Neonatal Medication Adminstration Sheet]</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">if Unknown</t>
+          <t xml:space="preserve">First dose time</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Infant given prophylaxis [NICU Admission Careform]</t>
+          <t xml:space="preserve">Frequency [Neonatal Medication Adminstration Sheet]</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Infant given prophylaxis</t>
+          <t xml:space="preserve">Frequency n</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">INTEGUMENTARY SYSTEM [NICU Admission Careform]</t>
+          <t xml:space="preserve">If other - specify name: [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">INTEGUMENTARY SYSTEM n</t>
+          <t xml:space="preserve">If other - specify name:</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labor was [NICU Admission Careform]</t>
+          <t xml:space="preserve">If yes - Apnea Prevention/Treatment Administered [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labor was</t>
+          <t xml:space="preserve">If yes - Apnea Prevention/Treatment Administered</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNMP known? [NICU Admission Careform]</t>
+          <t xml:space="preserve">If yes - select antibiotic(s) [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNMP known n</t>
+          <t xml:space="preserve">If yes - select antibiotic(s)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal medication during pregnancy and labor [NICU Admission Careform]</t>
+          <t xml:space="preserve">IV fluids administered? [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal medication during pregnancy and labor</t>
+          <t xml:space="preserve">IV fluids administered?</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal Status [NICU Admission Careform]</t>
+          <t xml:space="preserve">IV Fluids End date [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal Status</t>
+          <t xml:space="preserve">IV Fluids End date</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Membrane ruptured [NICU Admission Careform]</t>
+          <t xml:space="preserve">IV Fluids Start date [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Membrane ruptured</t>
+          <t xml:space="preserve">IV Fluids Start date</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mode of delivery [NICU Admission Careform]</t>
+          <t xml:space="preserve">Mechanical Ventilation End Date [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mode of delivery n</t>
+          <t xml:space="preserve">Mechanical Ventilation End Date</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mother HIV status [NICU Admission Careform]</t>
+          <t xml:space="preserve">Mechanical Ventilation End Time [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mother HIV status n</t>
+          <t xml:space="preserve">Mechanical Ventilation End Time</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mother's Age [NICU Admission Careform]</t>
+          <t xml:space="preserve">Mechanical Ventilation Start Date [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mother's Age</t>
+          <t xml:space="preserve">Mechanical Ventilation Start Date</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mother's educational status [NICU Admission Careform]</t>
+          <t xml:space="preserve">Mechanical Ventilation Start Time [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mothers educational status</t>
+          <t xml:space="preserve">Mechanical Ventilation Start Time</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mother's occupation [NICU Admission Careform]</t>
+          <t xml:space="preserve">Medication [Neonatal Medication Adminstration Sheet]</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mothers occupation</t>
+          <t xml:space="preserve">Medication n</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mother's Religion [NICU Admission Careform]</t>
+          <t xml:space="preserve">Medication Given [Neonatal Medication Adminstration Sheet]</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mothers religion n</t>
+          <t xml:space="preserve">Medication Given n</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mother’s Name [NICU Admission Careform]</t>
+          <t xml:space="preserve">Medication route [Neonatal Medication Adminstration Sheet]</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mothers Name</t>
+          <t xml:space="preserve">Medication route n</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">MUSCULOSKELETAL SYSTEM [NICU Admission Careform]</t>
+          <t xml:space="preserve">Oxygen saturation (%) level that led to the use of mechanical ventilation [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">MUSCULOSKELETAL SYSTEM</t>
+          <t xml:space="preserve">Oxygen saturation (%) level that led to the use of mechanical ventilation</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number of ANC visits [NICU Admission Careform]</t>
+          <t xml:space="preserve">Oxygen saturation (%) level that led to the use of oxygen therapy [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number of ANC visits n</t>
+          <t xml:space="preserve">Oxygen saturation (%) level that led to the use of oxygen therapy</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">number of doses [NICU Admission Careform]</t>
+          <t xml:space="preserve">Oxygen Therapy Administered? [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">number of tt doses</t>
+          <t xml:space="preserve">Oxygen Therapy Administered?</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number of stillbirths [NICU Admission Careform]</t>
+          <t xml:space="preserve">Oxygen Therapy End date [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number of stillbirths n</t>
+          <t xml:space="preserve">Oxygen Therapy End date</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">on HAART [NICU Admission Careform]</t>
+          <t xml:space="preserve">Oxygen Therapy End time [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">on HAART</t>
+          <t xml:space="preserve">Oxygen Therapy End time</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Para [NICU Admission Careform]</t>
+          <t xml:space="preserve">Oxygen Therapy Start date [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Para</t>
+          <t xml:space="preserve">Oxygen Therapy Start date</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phone Number 2: [NICU Admission Careform]</t>
+          <t xml:space="preserve">Oxygen Therapy Start time [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phone number n</t>
+          <t xml:space="preserve">Oxygen Therapy Start time</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phone number [NICU Admission Careform]</t>
+          <t xml:space="preserve">Phototherapy Administered? [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phone number n</t>
+          <t xml:space="preserve">Phototherapy Administered?</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Place of ANC follow up [NICU Admission Careform]</t>
+          <t xml:space="preserve">Phototherapy End date [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Place of ANC follow up</t>
+          <t xml:space="preserve">Phototherapy End date</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Place of delivery [NICU Admission Careform]</t>
+          <t xml:space="preserve">Phototherapy Start date [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Place of delivery</t>
+          <t xml:space="preserve">Phototherapy Start date</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Placed skin-to-skin at birth [NICU Admission Careform]</t>
+          <t xml:space="preserve">Prescribing doctor’s Name [Neonatal Medication Adminstration Sheet]</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Placed skin to skin at birth</t>
+          <t xml:space="preserve">Prescribing doctors Name</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reason for referral [NICU Admission Careform]</t>
+          <t xml:space="preserve">Remark [Neonatal Medication Adminstration Sheet]</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reason for referral adm</t>
+          <t xml:space="preserve">Remark n</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Received delayed cord clamping [NICU Admission Careform]</t>
+          <t xml:space="preserve">Start date [Neonatal Medication Adminstration Sheet]</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Received delayed cord clamping</t>
+          <t xml:space="preserve">Start date</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Referring health facility [NICU Admission Careform]</t>
+          <t xml:space="preserve">Time of Administration [Neonatal Medication Adminstration Sheet]</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Referring health facility</t>
+          <t xml:space="preserve">Time of Administration</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resuscitation in delivery room [NICU Admission Careform]</t>
+          <t xml:space="preserve">Time of Amikacin administration: [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resuscitation  in delivery room</t>
+          <t xml:space="preserve">Time of Amikacin administration:</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Significant events during current or previous pregnancy: [NICU Admission Careform]</t>
+          <t xml:space="preserve">Time of Amoxicillin administration: [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Significant events during current or previous pregnancy</t>
+          <t xml:space="preserve">Time of Amoxicillin administration:</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Specify Other medication [NICU Admission Careform]</t>
+          <t xml:space="preserve">Time of Ampicillin administration: [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Specify Other medication n</t>
+          <t xml:space="preserve">Time of Ampicillin administration:</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time of Admission [NICU Admission Careform]</t>
+          <t xml:space="preserve">Time of Benzathine Penicillin administration: [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time of Admission n</t>
+          <t xml:space="preserve">Time of Benzathine Penicillin administration:</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time of birth [NICU Admission Careform]</t>
+          <t xml:space="preserve">Time of Cefalexin administration: [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time of birth</t>
+          <t xml:space="preserve">Time of Cefalexin administration:</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Total downes score [NICU Admission Careform]</t>
+          <t xml:space="preserve">Time of Cefixime administration: [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Total downes score</t>
+          <t xml:space="preserve">Time of Cefixime administration:</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transferred to NICU with [NICU Admission Careform]</t>
+          <t xml:space="preserve">Time of Cefotaxime administration: [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transferred to NICU with</t>
+          <t xml:space="preserve">Time of Cefotaxime administration:</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Treatment [NICU Admission Careform]</t>
+          <t xml:space="preserve">Time of Ceftazidime administration: [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Treatment</t>
+          <t xml:space="preserve">Time of Ceftazidime administration:</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">TT Vaccine [NICU Admission Careform]</t>
+          <t xml:space="preserve">Time of Ceftriaxone administration: [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">TT Vaccine n</t>
+          <t xml:space="preserve">Time of Ceftriaxone administration:</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t xml:space="preserve">TTC eye ointment [NICU Admission Careform]</t>
+          <t xml:space="preserve">Time of Ciprofloxacin administration: [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">TTC eye ointment</t>
+          <t xml:space="preserve">Time of Ciprofloxacin administration:</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Admission Careform</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weight at admission (grams) [NICU Admission Careform]</t>
+          <t xml:space="preserve">Time of Clindamycin administration: [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weight at admission n</t>
+          <t xml:space="preserve">Time of Clindamycin administration:</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Air entry [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Time of Cloxacillin administration: [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Air entry</t>
+          <t xml:space="preserve">Time of Cloxacillin administration:</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Time of Crystalline Penicillin administration: [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment</t>
+          <t xml:space="preserve">Time of Crystalline Penicillin administration:</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowl sound [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Time of Flucloxacillin administration: [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowl sound</t>
+          <t xml:space="preserve">Time of Flucloxacillin administration:</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">capillary refill [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Time of Gentamicin administration: [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t xml:space="preserve">capillary refill</t>
+          <t xml:space="preserve">Time of Gentamicin administration:</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Color of Vomiting [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Time of Levofloxacin administration: [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Color of Vomiting</t>
+          <t xml:space="preserve">Time of Levofloxacin administration:</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Culture done? [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Time of Meropenem administration: [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Culture done</t>
+          <t xml:space="preserve">Time of Meropenem administration:</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">culture growth [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Time of Metronidazole administration: [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve">culture growth</t>
+          <t xml:space="preserve">Time of Metronidazole administration:</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date and Time [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Time of OTHER antibiotic administration: [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date and Time</t>
+          <t xml:space="preserve">Time of OTHER antibiotic administration:</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Day of life [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Time of Piperazine administration: [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Day of life</t>
+          <t xml:space="preserve">Time of Piperazine administration:</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diagnosis [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Time of Tazobactam administration: [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diagnosis n</t>
+          <t xml:space="preserve">Time of Tazobactam administration:</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t xml:space="preserve">distention [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Time of Vancomycin administration: [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t xml:space="preserve">distention</t>
+          <t xml:space="preserve">Time of Vancomycin administration:</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Down’s score [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Transfusion date [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Down’s score</t>
+          <t xml:space="preserve">Transfusion date</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Medication and intervention</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Echo [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Transfusion given? [Neonatal Intervention Sheet]</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Echo</t>
+          <t xml:space="preserve">Transfusion given?</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t xml:space="preserve">General appearance [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Abortion (Induced) [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t xml:space="preserve">General appearance</t>
+          <t xml:space="preserve">Abortion (Induced) ref</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t xml:space="preserve">HC [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Abortion (Spontaneous) [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t xml:space="preserve">HC</t>
+          <t xml:space="preserve">Abortion (Spontaneous) ref</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heart sound [NICU Progress Care Form]</t>
+          <t xml:space="preserve">ANC Visit [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heart sound</t>
+          <t xml:space="preserve">ANC Visit ref</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t xml:space="preserve">IVF received? [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Anti D given [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t xml:space="preserve">IVF received</t>
+          <t xml:space="preserve">Anti D given ref</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaundice [NICU Progress Care Form]</t>
+          <t xml:space="preserve">APGAR score: 10th min [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaundice</t>
+          <t xml:space="preserve">APGAR score: 10th min</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t xml:space="preserve">last culture date [NICU Progress Care Form]</t>
+          <t xml:space="preserve">APGAR score: 1st min [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t xml:space="preserve">last culture date</t>
+          <t xml:space="preserve">APGAR score: 1st min</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Level of jaundice [NICU Progress Care Form]</t>
+          <t xml:space="preserve">APGAR score: 20th min [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Level of jaundice</t>
+          <t xml:space="preserve">APGAR score: 20th min</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mental status [NICU Progress Care Form]</t>
+          <t xml:space="preserve">APGAR score: 5th min [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mental status</t>
+          <t xml:space="preserve">APGAR score: 5th min</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t xml:space="preserve">ml/kg/day [NICU Progress Care Form]</t>
+          <t xml:space="preserve">ARV drugs [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t xml:space="preserve">ml/kg/day</t>
+          <t xml:space="preserve">ARV drugs ref</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name of physician [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Baby dried thoroughly at birth [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name of physician n</t>
+          <t xml:space="preserve">Baby dried thoroughly at birth</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t xml:space="preserve">New concern/complaint [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Baby placed in iKMC [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t xml:space="preserve">New concern/complaint</t>
+          <t xml:space="preserve">Baby placed in iKMC</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Organomegaly [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Baby placed in plastic bag [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Organomegaly</t>
+          <t xml:space="preserve">Baby placed in plastic bag</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Assessment [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Baby placed on CPAP [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Assessment</t>
+          <t xml:space="preserve">Baby placed on CPAP</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pain Score [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Baby placed skin to skin at birth [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pain Score</t>
+          <t xml:space="preserve">Baby placed skin to skin at birth</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t xml:space="preserve">primitive reflex: Grasp [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Bag and Mask [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t xml:space="preserve">primitive reflex: Grasp</t>
+          <t xml:space="preserve">Bag and Mask</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t xml:space="preserve">primitive reflex: Moro [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Ballard Score [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t xml:space="preserve">primitive reflex: Moro</t>
+          <t xml:space="preserve">Ballard Score ref</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t xml:space="preserve">primitive reflex: Suckling [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Blood group done [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t xml:space="preserve">primitive reflex: Suckling</t>
+          <t xml:space="preserve">Blood group done ref</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx [NICU Progress Care Form]</t>
+          <t xml:space="preserve">CD4/date [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">CD4/date ref</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t xml:space="preserve">sensitivity [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Chest compression [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t xml:space="preserve">sensitivity</t>
+          <t xml:space="preserve">Chest compression</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sign of respiratory distress [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Chlorhexdine 4% [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sign of respiratory distress</t>
+          <t xml:space="preserve">Chlorhexdine 4%</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Specify other sign of respiratiory distress [NICU Progress Care Form]</t>
+          <t xml:space="preserve">COOMB’S test [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Specify other sign of respiratiory distress n</t>
+          <t xml:space="preserve">COOMB’S test ref</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stool [NICU Progress Care Form]</t>
+          <t xml:space="preserve">date completed [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stool</t>
+          <t xml:space="preserve">date completed ref</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t xml:space="preserve">TF ordered total/intake (ml/kg/day) [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Date of referral [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t xml:space="preserve">TF ordered total/intake (ml/kg/day)</t>
+          <t xml:space="preserve">Date of referral</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Type of feeding [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Delayed Cord clamping done [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Type of feeding</t>
+          <t xml:space="preserve">Delayed Cord clamping done</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Type of respiratory support [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Delivery [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Type of respiratory support</t>
+          <t xml:space="preserve">Delivery n</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICU Progress Care Form</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vomiting [NICU Progress Care Form]</t>
+          <t xml:space="preserve">Delivery attended by provider trained on HBB/ neonatal resuscitation? [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vomiting</t>
+          <t xml:space="preserve">Delivery attended by provider trained on HBB/ neonatal resuscitation</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Active DX [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">Duration [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Active DX</t>
+          <t xml:space="preserve">Duration n</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alertness Routine reflexes [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">Duration of resuscitation [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alertness Routine reflexes</t>
+          <t xml:space="preserve">Duration of resuscitation</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANC [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">Duration of ROM [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANC</t>
+          <t xml:space="preserve">Duration of ROM</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antibiotics /Days [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">Early Neonatal death [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antibiotics /Days</t>
+          <t xml:space="preserve">Early Neonatal death ref</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convulsion Apnea [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">Epinephrine doses [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convulsion Apnea</t>
+          <t xml:space="preserve">Epinephrine doses</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t xml:space="preserve">CPAP, LFNC, IPPV, HFOV [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">Estimated by: Obstetric Ultrasound [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t xml:space="preserve">CPAP, LFNC, IPPV, HFOV</t>
+          <t xml:space="preserve">Estimated by: Obstetric Ultrasound ref</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRP [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">Feeding initiated [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRP</t>
+          <t xml:space="preserve">Feeding initiated</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRT [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">Fluid administered [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRT</t>
+          <t xml:space="preserve">Fluid administered</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t xml:space="preserve">CSF [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">Fundal height [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t xml:space="preserve">CSF</t>
+          <t xml:space="preserve">Fundal height ref</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUS(Cranial U/S) [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">Gestational age (days) [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUS(Cranial U/S)</t>
+          <t xml:space="preserve">Gestational age (days) ref</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Day of life / GA /cGA [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">Gestational age (weeks) [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Day of life / GA /cGA</t>
+          <t xml:space="preserve">Gestational age (weeks) ref</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Days on phototherapy [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">HBsAg [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Days on phototherapy</t>
+          <t xml:space="preserve">HBsAg ref</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Down score [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">If done tick what was done [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Down score</t>
+          <t xml:space="preserve">If done tick what was done</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t xml:space="preserve">EBM/Formula/ Fortification Bolus/Continuous [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">If Obstetric Ultrasound, done at ref [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t xml:space="preserve">EBM/Formula/ Fortification Bolus/Continuous</t>
+          <t xml:space="preserve">If Obstetric Ultrasound, done at ref</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Examination [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">If yes Duration [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Examination</t>
+          <t xml:space="preserve">If yes Duration ref</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Examination ref prog [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">If yes, number of doses [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Examination ref prog</t>
+          <t xml:space="preserve">If yes, number of doses ref</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exchange value [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">If yes, on HAART [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exchange value</t>
+          <t xml:space="preserve">If yes, on HAART ref</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hb /date Last BT/ Transfusion cut of point [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">Indication [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hb /date Last BT/ Transfusion cut of point</t>
+          <t xml:space="preserve">Indication n</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iron supplement [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">Infant prophylaxis started [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iron supplement</t>
+          <t xml:space="preserve">Infant prophylaxis started ref</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t xml:space="preserve">IV  Line Present [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">Intra/Inter facility transfer [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t xml:space="preserve">IV  Line Present</t>
+          <t xml:space="preserve">Intra/Inter facility transfer</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Last Culture date [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">Investigation result [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Last Culture date</t>
+          <t xml:space="preserve">Investigation result</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t xml:space="preserve">NGT/OGT/cup/ Direct BF [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">Labour [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t xml:space="preserve">NGT/OGT/cup/ Direct BF</t>
+          <t xml:space="preserve">Labour n</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t xml:space="preserve">NPO/Open drainage [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">LNMP [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t xml:space="preserve">NPO/Open drainage</t>
+          <t xml:space="preserve">LNMP ref</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Organism [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">Maternal Age [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Organism</t>
+          <t xml:space="preserve">Maternal Age n</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Others Medication [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">Maternal MRN [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Others Medication</t>
+          <t xml:space="preserve">Maternal MRN n</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phototherapy value [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">Meconium sucked from oropharynx [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phototherapy value</t>
+          <t xml:space="preserve">Meconium sucked from oropharynx</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLT [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">Mother PICT [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLT</t>
+          <t xml:space="preserve">Mother PICT ref</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Precordial exam [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">Name of clinician [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Precordial exam</t>
+          <t xml:space="preserve">Name of clinician</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resolved DX [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">Name of Referring Facility [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resolved DX</t>
+          <t xml:space="preserve">Name of Referring Facility</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sensitivity [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">Neonatal resuscitation done [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sensitivity</t>
+          <t xml:space="preserve">Neonatal resuscitation done</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Site / Infiltration [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">Other treatment given [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Site / Infiltration</t>
+          <t xml:space="preserve">Other treatment given</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skin Color (Jaundice, Pallor…) [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">Para [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skin Color (Jaundice, Pallor…)</t>
+          <t xml:space="preserve">Para ref</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stool/color [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">place of ANC follow up [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stool/color</t>
+          <t xml:space="preserve">place of ANC follow up ref</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t xml:space="preserve">TFI/IV/Feeding [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">Pregnancy related maternal problem [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t xml:space="preserve">TFI/IV/Feeding</t>
+          <t xml:space="preserve">Pregnancy related maternal problem ref</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t xml:space="preserve">TSB/D   or TCB [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">Reason for NICU referral [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t xml:space="preserve">TSB/D   or TCB</t>
+          <t xml:space="preserve">Reason for NICU referral</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Type of Fluid [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">RH [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Type of Fluid</t>
+          <t xml:space="preserve">RH ref</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wt/Na/K/RFT [Progress care form for Referral Hospitals]</t>
+          <t xml:space="preserve">Singleton-Multiple [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wt/Na/K/RFT</t>
+          <t xml:space="preserve">Singleton-Multiple</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tracked Entity Attributes</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t xml:space="preserve">first_name</t>
+          <t xml:space="preserve">Stillbirth [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonate First Name</t>
+          <t xml:space="preserve">Stillbirth ref</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tracked Entity Attributes</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t xml:space="preserve">family_name</t>
+          <t xml:space="preserve">Transferred to [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonate Last Name</t>
+          <t xml:space="preserve">Transferred to</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tracked Entity Attributes</t>
+          <t xml:space="preserve">Neonatal referral form</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_id</t>
+          <t xml:space="preserve">TT vaccine [Neonatal referral form]</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonate MRN</t>
+          <t xml:space="preserve">TT vaccine ref</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
+          <t xml:space="preserve">Neonatal referral form</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TTC Eye prophylaxis given [Neonatal referral form]</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TTC Eye prophylaxis given</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neonatal referral form</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VDRL [Neonatal referral form]</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VDRL ref</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neonatal referral form</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VDRL Treatment [Neonatal referral form]</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VDRL Treatment ref</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neonatal referral form</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Viral load/date [Neonatal referral form]</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Viral load/date ref</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neonatal referral form</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vital signs on referral HR [Neonatal referral form]</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vital signs on referral HR</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neonatal referral form</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vital signs on referral RR [Neonatal referral form]</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vital signs on referral RR</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neonatal referral form</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vital signs on referral Saturation [Neonatal referral form]</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vital signs on referral Saturation</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neonatal referral form</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vital signs on referral Temp (c) [Neonatal referral form]</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vital signs on referral Temp (c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neonatal referral form</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vitamin K given [Neonatal referral form]</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vitamin K given</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abdomen [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abdomen n</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abortion(Induced) [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abortion(Induced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abortion(Spontaneous) [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abortion(Spontaneous)</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admission age (Minutes/hours/days) [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admission age</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admission age unit [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admission age unit n</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">amenorrheic for how many months [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">amenorrheic for how many months</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amniotic fluid was [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amniotic fluid was</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANC visit [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANC visit</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Any abnormality from System Examination? [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Any abnormality from System Examination</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APGAR score 10th min [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APGAR score 10th min</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APGAR score 1st min [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APGAR score 1st min</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APGAR score 5th min [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APGAR score 5th min</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APGAR score known? [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APGAR score known</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asphyxia [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asphyxia</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asphyxia stage [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asphyxia stage</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ballard score [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ballard score</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Birth Weight (grams) [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Birth Weight n</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Birth weight category [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Birth weight category</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blood group and Rh [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blood group and Rh n</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Breastfeeding initiated within 1 hr of birth [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Breastfeeding initiated within 1 hr of birth</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CENTRAL NERVOUS SYSTEM [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CENTRAL NERVOUS SYSTEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHEST [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHEST n</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cord Chlorhexidine Administered [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cord Chlorhexidine Administered</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CVS [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CVS adm n</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date of Admission [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date of Admission n</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date of delivery [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date of delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Day/Night Local time [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Day/Night Local time</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Downes: Air Entry [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Downes Air Entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Downes: Cyanosis [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Downes Cyanosis</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Downes: Grunting [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Downes Grunting</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Downes: Respiratory Rate [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Downes Respiratory Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Downes: Retractions [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Downes Retractions</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Duration of rapture of membrane (in hrs) [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Duration of rapture of membrane</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dysmorphic feature [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dysmorphic feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dysmorphysim [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dysmorphysim</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GA by U/S [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GA by U/S</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">General appearance [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">General appearance</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GENITALIA [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GENITALIA n</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HBsAg [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HBsAg n</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Head circumference (cm) [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Head circumference n</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEENT [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEENT n</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hours prior to delivery [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hours prior to delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HR (beats/min) [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HR at admission</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If Resuscitated, tick what was done [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If Resuscitated, tick what was done</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">if Unknown [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">if Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Infant given prophylaxis [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Infant given prophylaxis</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INTEGUMENTARY SYSTEM [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INTEGUMENTARY SYSTEM n</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebele [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Address of the mother Kebele</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Labor was [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Labor was</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lasted for_____hrs [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lasted for</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (cm) [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length n</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LGS [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LGS n</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNMP [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNMP n</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNMP known? [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNMP known n</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maternal medication during pregnancy and labor [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maternal medication during pregnancy and labor</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maternal Status [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maternal Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Membrane ruptured [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Membrane ruptured</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mode of delivery [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mode of delivery n</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mother HIV status [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mother HIV status n</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mother's Age [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mother's Age</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mother's educational status [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mothers educational status</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mother's occupation [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mothers occupation</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mother's Religion [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mothers religion n</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mother’s Name [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mothers Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MUSCULOSKELETAL SYSTEM [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MUSCULOSKELETAL SYSTEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NECK [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NECK n</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NLT or DLT [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time of birth NLT or DLT n</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Number of ANC visits [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Number of ANC visits n</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">number of doses [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">number of tt doses</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Number of stillbirths [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Number of stillbirths n</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">on HAART [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">on HAART</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other significant events [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other significant events during current or previous pregnancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Para [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Para</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phone Number 2: [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phone number n</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phone number [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phone number n</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Place of ANC follow up [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Place of ANC follow up</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Place of delivery [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Place of delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Placed skin-to-skin at birth [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Placed skin to skin at birth</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plan [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plan n</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason for referral [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason for referral adm</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Received delayed cord clamping [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Received delayed cord clamping</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referring health facility [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referring health facility</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resuscitation in delivery room [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resuscitation  in delivery room</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RR (breaths/min) [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RR at admission</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Significant events during current or previous pregnancy: [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Significant events during current or previous pregnancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Specify Other medication [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Specify Other medication n</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SpO2 [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SpO2 at admission</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temp (C) [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temp at admission</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time of Admission [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time of Admission n</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time of birth [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time of birth</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total downes score [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total downes score</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transferred to NICU with [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transferred to NICU with</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Treatment [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Treatment</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TT Vaccine [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TT Vaccine n</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TTC eye ointment [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TTC eye ointment</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VDRL [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VDRL n</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vitamin K given [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vitamin K given birth</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Weight at admission (grams) [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Weight at admission n</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wereda [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Address of the mother Wereda</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Admission Careform</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone [NICU Admission Careform]</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Address of the mother Zone</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Air entry [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Air entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assessment [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assessment</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bowl sound [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bowl sound</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">capillary refill [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">capillary refill</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Color of Vomiting [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Color of Vomiting</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Culture done? [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Culture done</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">culture growth [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">culture growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date and Time [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date and Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Day of life [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Day of life</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diagnosis [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diagnosis n</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">distention [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">distention</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Down’s score [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Down’s score</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Echo [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Echo</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">General appearance [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">General appearance</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heart sound [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heart sound</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HR [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HR n</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IVF received? [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IVF received</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jaundice [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jaundice</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">last culture date [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">last culture date</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Level of jaundice [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Level of jaundice</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mental status [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mental status</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ml/kg/day [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ml/kg/day</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name of physician [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name of physician n</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New concern/complaint [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New concern/complaint</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organomegaly [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organomegaly</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other Assessment [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other Assessment</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pain Score [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pain Score</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plan [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plan n</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">primitive reflex: Grasp [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">primitive reflex: Grasp</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">primitive reflex: Moro [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">primitive reflex: Moro</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">primitive reflex: Suckling [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">primitive reflex: Suckling</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RR [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RR n</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rx [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rx</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sensitivity [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sensitivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sign of respiratory distress [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sign of respiratory distress</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Specify other sign of respiratiory distress [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Specify other sign of respiratiory distress n</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spo2 [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spo2 n</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stool [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stool</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temp [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temp n</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TF ordered total/intake (ml/kg/day) [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TF ordered total/intake (ml/kg/day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type of feeding [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type of feeding</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type of respiratory support [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type of respiratory support</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Urine out put (ml/kg/hr) [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Urine out put</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vomiting [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vomiting</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICU Progress Care Form</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Weight [NICU Progress Care Form]</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Weight n</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amount of oxygen (FiO2) [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amount of oxygen (FiO2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blood culture [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blood culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Changed weight [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Changed weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current weight [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Downes’ Score [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Downes’ Score</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Family Involvement [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Family Involvement</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heart Rate [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heart Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hrs on KMC [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hrs on KMC</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV line check [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV line check</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kmc done? [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kmc done</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lab blood draw [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lab blood draw</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medications Given [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medications Given</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mode of feeding [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mode of feeding</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse Initials&amp; signature [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse Initials&amp; signature</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organism [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organism n</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oxygen Saturation [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oxygen Saturation</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oxygen Source [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oxygen Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pain score [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pain score</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phototherapy [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phototherapy n</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBS [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBS</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remarks [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Respiratory Rate [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Respiratory Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sensitivity [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sensitivity n</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stool [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stool n</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temperature [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temperature n</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time of check [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time of check</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UOP [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vomiting [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vomiting n</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weight (Change) [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weight (Change)</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurse followup Sheet</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Who is doing KMC(Mother/Surrogate) [Neonatal Nurse followup Sheet]</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Who is doing KMC(Mother/Surrogate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active DX [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active DX</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alertness Routine reflexes [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alertness Routine reflexes</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANC [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANC</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Antibiotics /Days [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Antibiotics /Days</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assessment [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assessment ref prog</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP ref prog</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convulsion Apnea [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convulsion Apnea</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAP, LFNC, IPPV, HFOV [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAP, LFNC, IPPV, HFOV</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CRP [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CRP</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CRT [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSF [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CUS(Cranial U/S) [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CUS(Cranial U/S)</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Day of life / GA /cGA [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Day of life / GA /cGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Days on phototherapy [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Days on phototherapy</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diagnosis [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diagnosis ref prog</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Down score [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Down score</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EBM/Formula/ Fortification Bolus/Continuous [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EBM/Formula/ Fortification Bolus/Continuous</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Echo [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Echo  ref prog</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Examination [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Examination</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Examination ref prog [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Examination ref prog</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exchange value [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exchange value</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hb /date Last BT/ Transfusion cut of point [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hb /date Last BT/ Transfusion cut of point</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIE Score [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIE Score ref prog</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HR [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HR ref prg</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Iron supplement [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Iron supplement</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV  Line Present [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV  Line Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Last Culture date [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Last Culture date</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name &amp; Signature [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name and Signature ref prog</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NGT/OGT/cup/ Direct BF [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NGT/OGT/cup/ Direct BF</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NPO/Open drainage [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NPO/Open drainage</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organism [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organism</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Others Medication [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Others Medication</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pain score [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pain score ref prog</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phototherapy value [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phototherapy value</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plan [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plan ref prog</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLT [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLT</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Precordial exam [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Precordial exam</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resolved DX [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resolved DX</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RR [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RR ref prog</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sensitivity [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sensitivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Site / Infiltration [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Site / Infiltration</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Skin Color (Jaundice, Pallor…) [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Skin Color (Jaundice, Pallor…)</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SpO2 [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SpO2 ref prog</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stool/color [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stool/color</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temperature [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temperature ref prog</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TFI/IV/Feeding [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TFI/IV/Feeding</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Treatment [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Treatment ref prog</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSB/D   or TCB [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSB/D   or TCB</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type of Fluid [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type of Fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UOP [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UOP ref prg</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vomiting [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vomiting ref prog</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WBC [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WBC ref prog</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress care form for Referral Hospitals</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wt/Na/K/RFT [Progress care form for Referral Hospitals]</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wt/Na/K/RFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tracked Entity Attributes</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
+      <c r="B482" t="inlineStr">
+        <is>
+          <t xml:space="preserve">family_name</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neonate Last Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tracked Entity Attributes</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t xml:space="preserve">first_name</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neonate First Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tracked Entity Attributes</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
         <is>
           <t xml:space="preserve">gender</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr">
+      <c r="C484" t="inlineStr">
         <is>
           <t xml:space="preserve">Neonate sex</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tracked Entity Attributes</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_id</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neonate MRN</t>
         </is>
       </c>
     </row>
